--- a/template-soal.xlsx
+++ b/template-soal.xlsx
@@ -55,9 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -435,7 +438,8 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,96 +493,103 @@
           <t>Pembahasan</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Gambar</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Lapisan bumi yang paling tebal adalah …</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Kerak</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Mantel</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Inti luar</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Inti dalam</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Mantel ±2.900 km, lapisan paling tebal.</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Gempa tektonik disebabkan oleh …</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Letusan gunung api</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Runtuhnya gua</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Pergerakan lempeng</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ledakan nuklir</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Meteor</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Pergerakan lempeng melepas energi.</t>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Perhatikan gambar! Lapisan yang ditandai huruf B adalah …</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Kerak</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mantel</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Inti luar</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Inti dalam</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Contoh soal bergambar: isi kolom Gambar dengan nama file di folder gambar/ atau link https://</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>lapisan-bumi.png</t>
         </is>
       </c>
     </row>
